--- a/output/upload/S00026_2129_상속H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2129_상속H종신보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>21291</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1386,11 +1406,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>21291</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1468,11 +1508,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>21291</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1550,31 +1610,83 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>21291</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
+      <c r="J10" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="6" t="n"/>
-      <c r="Q10" s="6" t="n"/>
+      <c r="O10" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R10" s="6" t="n"/>
       <c r="S10" s="6" t="n"/>
       <c r="T10" s="6" t="n"/>
       <c r="U10" s="6" t="n"/>
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
-      <c r="X10" s="6" t="n"/>
-      <c r="Y10" s="6" t="n"/>
-      <c r="Z10" s="6" t="n"/>
+      <c r="X10" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA10" s="6" t="n"/>
       <c r="AB10" s="6" t="n"/>
       <c r="AC10" s="6" t="n"/>
@@ -1600,31 +1712,83 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>21291</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
+      <c r="J11" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="6" t="n"/>
+      <c r="O11" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R11" s="6" t="n"/>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n"/>
-      <c r="Y11" s="6" t="n"/>
-      <c r="Z11" s="6" t="n"/>
+      <c r="X11" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y11" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z11" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA11" s="6" t="n"/>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
@@ -1650,31 +1814,83 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>21291</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
+      <c r="J12" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="6" t="n"/>
+      <c r="O12" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n"/>
-      <c r="Y12" s="6" t="n"/>
-      <c r="Z12" s="6" t="n"/>
+      <c r="X12" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y12" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA12" s="6" t="n"/>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>

--- a/output/upload/S00026_2129_상속H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2129_상속H종신보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>2129001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>2129001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>2129001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>2129001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>2129001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>2129001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">

--- a/output/upload/S00026_2129_상속H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2129_상속H종신보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV22"/>
+  <dimension ref="A1:AV26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1381,7 +1381,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA7" s="6" t="n"/>
+      <c r="AA7" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB7" s="6" t="n"/>
       <c r="AC7" s="6" t="n"/>
       <c r="AD7" s="6" t="n"/>
@@ -1446,7 +1450,7 @@
         <v>15</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
@@ -1473,17 +1477,21 @@
       <c r="V8" s="6" t="n"/>
       <c r="W8" s="6" t="n"/>
       <c r="X8" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y8" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z8" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AA8" s="6" t="n"/>
+      <c r="AA8" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB8" s="6" t="n"/>
       <c r="AC8" s="6" t="n"/>
       <c r="AD8" s="6" t="n"/>
@@ -1548,7 +1556,7 @@
         <v>15</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
@@ -1575,17 +1583,21 @@
       <c r="V9" s="6" t="n"/>
       <c r="W9" s="6" t="n"/>
       <c r="X9" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y9" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AA9" s="6" t="n"/>
+      <c r="AA9" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB9" s="6" t="n"/>
       <c r="AC9" s="6" t="n"/>
       <c r="AD9" s="6" t="n"/>
@@ -1647,10 +1659,10 @@
       </c>
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
@@ -1687,7 +1699,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA10" s="6" t="n"/>
+      <c r="AA10" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB10" s="6" t="n"/>
       <c r="AC10" s="6" t="n"/>
       <c r="AD10" s="6" t="n"/>
@@ -1749,7 +1765,7 @@
       </c>
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>68</v>
@@ -1789,7 +1805,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA11" s="6" t="n"/>
+      <c r="AA11" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
       <c r="AD11" s="6" t="n"/>
@@ -1851,10 +1871,10 @@
       </c>
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
@@ -1881,17 +1901,21 @@
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
       <c r="X12" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y12" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z12" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="n"/>
+      <c r="AA12" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>
       <c r="AD12" s="6" t="n"/>
@@ -1916,32 +1940,88 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
+      <c r="O13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n"/>
-      <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
-      <c r="AA13" s="6" t="n"/>
+      <c r="X13" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
       <c r="AD13" s="6" t="n"/>
@@ -1966,32 +2046,88 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="6" t="n"/>
+      <c r="O14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n"/>
-      <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
-      <c r="AA14" s="6" t="n"/>
+      <c r="X14" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA14" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
       <c r="AD14" s="6" t="n"/>
@@ -2016,32 +2152,88 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="J15" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
+      <c r="O15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n"/>
-      <c r="Y15" s="6" t="n"/>
-      <c r="Z15" s="6" t="n"/>
-      <c r="AA15" s="6" t="n"/>
+      <c r="X15" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z15" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA15" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
       <c r="AD15" s="6" t="n"/>
@@ -2066,32 +2258,88 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="J16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="6" t="n"/>
+      <c r="O16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n"/>
-      <c r="Y16" s="6" t="n"/>
-      <c r="Z16" s="6" t="n"/>
-      <c r="AA16" s="6" t="n"/>
+      <c r="X16" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z16" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA16" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
       <c r="AD16" s="6" t="n"/>
@@ -2116,32 +2364,88 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
+      <c r="J17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="6" t="n"/>
+      <c r="O17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n"/>
-      <c r="Y17" s="6" t="n"/>
-      <c r="Z17" s="6" t="n"/>
-      <c r="AA17" s="6" t="n"/>
+      <c r="X17" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y17" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z17" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA17" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
       <c r="AD17" s="6" t="n"/>
@@ -2166,32 +2470,88 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="J18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="6" t="n"/>
+      <c r="O18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n"/>
-      <c r="Y18" s="6" t="n"/>
-      <c r="Z18" s="6" t="n"/>
-      <c r="AA18" s="6" t="n"/>
+      <c r="X18" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y18" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z18" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA18" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
       <c r="AD18" s="6" t="n"/>
@@ -2216,32 +2576,88 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
+      <c r="J19" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="6" t="n"/>
+      <c r="O19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R19" s="6" t="n"/>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
-      <c r="X19" s="6" t="n"/>
-      <c r="Y19" s="6" t="n"/>
-      <c r="Z19" s="6" t="n"/>
-      <c r="AA19" s="6" t="n"/>
+      <c r="X19" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y19" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z19" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA19" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB19" s="6" t="n"/>
       <c r="AC19" s="6" t="n"/>
       <c r="AD19" s="6" t="n"/>
@@ -2266,32 +2682,88 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="J20" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="6" t="n"/>
+      <c r="O20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
-      <c r="X20" s="6" t="n"/>
-      <c r="Y20" s="6" t="n"/>
-      <c r="Z20" s="6" t="n"/>
-      <c r="AA20" s="6" t="n"/>
+      <c r="X20" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y20" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z20" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA20" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB20" s="6" t="n"/>
       <c r="AC20" s="6" t="n"/>
       <c r="AD20" s="6" t="n"/>
@@ -2316,32 +2788,88 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
+      <c r="J21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
+      <c r="O21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n"/>
-      <c r="Y21" s="6" t="n"/>
-      <c r="Z21" s="6" t="n"/>
-      <c r="AA21" s="6" t="n"/>
+      <c r="X21" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z21" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA21" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB21" s="6" t="n"/>
       <c r="AC21" s="6" t="n"/>
       <c r="AD21" s="6" t="n"/>
@@ -2366,32 +2894,88 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
+      <c r="J22" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
+      <c r="O22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R22" s="6" t="n"/>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
-      <c r="AA22" s="6" t="n"/>
+      <c r="X22" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y22" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z22" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA22" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB22" s="6" t="n"/>
       <c r="AC22" s="6" t="n"/>
       <c r="AD22" s="6" t="n"/>
@@ -2414,6 +2998,306 @@
       <c r="AU22" s="6" t="n"/>
       <c r="AV22" s="6" t="n"/>
     </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>20</v>
+      </c>
+      <c r="K23" t="n">
+        <v>68</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>999</v>
+      </c>
+      <c r="P23" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>20</v>
+      </c>
+      <c r="K24" t="n">
+        <v>72</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>999</v>
+      </c>
+      <c r="P24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>20</v>
+      </c>
+      <c r="K25" t="n">
+        <v>68</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>999</v>
+      </c>
+      <c r="P25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2129A01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2129001</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" t="n">
+        <v>72</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>999</v>
+      </c>
+      <c r="P26" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="L3:AV3"/>

--- a/output/upload/S00026_2129_상속H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2129_상속H종신보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV26"/>
+  <dimension ref="A1:AV38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1556,7 +1556,7 @@
         <v>15</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
       <c r="V9" s="6" t="n"/>
       <c r="W9" s="6" t="n"/>
       <c r="X9" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y9" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>15</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
@@ -1689,10 +1689,10 @@
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
       <c r="X10" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y10" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z10" s="6" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
       <c r="X11" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y11" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
@@ -1901,10 +1901,10 @@
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
       <c r="X12" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y12" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z12" s="6" t="inlineStr">
         <is>
@@ -1977,10 +1977,10 @@
       </c>
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
       <c r="X13" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y13" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z13" s="6" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
       </c>
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
       <c r="X14" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y14" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z14" s="6" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>68</v>
@@ -2219,10 +2219,10 @@
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
       <c r="X15" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y15" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z15" s="6" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>72</v>
@@ -2325,10 +2325,10 @@
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
       <c r="X16" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y16" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z16" s="6" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>68</v>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>72</v>
@@ -2578,22 +2578,22 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>80</v>
@@ -2684,22 +2684,22 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>80</v>
@@ -2790,22 +2790,22 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2825,10 +2825,10 @@
       </c>
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
       <c r="X21" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y21" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z21" s="6" t="inlineStr">
         <is>
@@ -2896,22 +2896,22 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2931,10 +2931,10 @@
       </c>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
@@ -2961,10 +2961,10 @@
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
       <c r="X22" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y22" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z22" s="6" t="inlineStr">
         <is>
@@ -3001,22 +3001,22 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
         <v>68</v>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -3076,22 +3076,22 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
         <v>72</v>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="X24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3151,22 +3151,22 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3188,7 +3188,7 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="X25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3226,22 +3226,22 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3263,36 +3263,936 @@
         <v>20</v>
       </c>
       <c r="K26" t="n">
+        <v>80</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>999</v>
+      </c>
+      <c r="P26" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2129A02</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2129002</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>20</v>
+      </c>
+      <c r="K27" t="n">
+        <v>68</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>999</v>
+      </c>
+      <c r="P27" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2129A02</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2129002</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>20</v>
+      </c>
+      <c r="K28" t="n">
         <v>72</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
       </c>
-      <c r="O26" t="n">
-        <v>999</v>
-      </c>
-      <c r="P26" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q26" t="inlineStr">
+      <c r="O28" t="n">
+        <v>999</v>
+      </c>
+      <c r="P28" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="X26" t="n">
+      <c r="X28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2129A02</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2129002</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
         <v>20</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="K29" t="n">
+        <v>68</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>999</v>
+      </c>
+      <c r="P29" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
         <v>20</v>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Y29" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2129A02</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2129002</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>20</v>
+      </c>
+      <c r="K30" t="n">
+        <v>72</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>999</v>
+      </c>
+      <c r="P30" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2129A03</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2129003</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>15</v>
+      </c>
+      <c r="K31" t="n">
+        <v>74</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>999</v>
+      </c>
+      <c r="P31" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2129A03</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2129003</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>15</v>
+      </c>
+      <c r="K32" t="n">
+        <v>78</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>999</v>
+      </c>
+      <c r="P32" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2129A03</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2129003</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>20</v>
+      </c>
+      <c r="K33" t="n">
+        <v>74</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>999</v>
+      </c>
+      <c r="P33" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2129A03</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2129003</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>20</v>
+      </c>
+      <c r="K34" t="n">
+        <v>78</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>999</v>
+      </c>
+      <c r="P34" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2129A04</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2129004</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>15</v>
+      </c>
+      <c r="K35" t="n">
+        <v>74</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>999</v>
+      </c>
+      <c r="P35" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2129A04</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2129004</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>15</v>
+      </c>
+      <c r="K36" t="n">
+        <v>78</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>999</v>
+      </c>
+      <c r="P36" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2129A04</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2129004</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>20</v>
+      </c>
+      <c r="K37" t="n">
+        <v>74</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>999</v>
+      </c>
+      <c r="P37" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2129A04</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2129004</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>20</v>
+      </c>
+      <c r="K38" t="n">
+        <v>78</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>999</v>
+      </c>
+      <c r="P38" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
         <is>
           <t>2</t>
         </is>

--- a/output/upload/S00026_2129_상속H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2129_상속H종신보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV38"/>
+  <dimension ref="A1:AV30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1339,7 +1339,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="n">
         <v>15</v>
       </c>
@@ -1445,7 +1449,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="n">
         <v>15</v>
       </c>
@@ -1551,7 +1559,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J9" s="6" t="n">
         <v>15</v>
       </c>
@@ -1657,7 +1669,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J10" s="6" t="n">
         <v>15</v>
       </c>
@@ -1763,7 +1779,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J11" s="6" t="n">
         <v>15</v>
       </c>
@@ -1869,7 +1889,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J12" s="6" t="n">
         <v>15</v>
       </c>
@@ -1942,22 +1966,22 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1975,7 +1999,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J13" s="6" t="n">
         <v>20</v>
       </c>
@@ -2048,22 +2076,22 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -2081,7 +2109,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J14" s="6" t="n">
         <v>20</v>
       </c>
@@ -2154,22 +2186,22 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -2187,7 +2219,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I15" s="6" t="n"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J15" s="6" t="n">
         <v>20</v>
       </c>
@@ -2260,22 +2296,22 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2293,7 +2329,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J16" s="6" t="n">
         <v>20</v>
       </c>
@@ -2366,22 +2406,22 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2399,7 +2439,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I17" s="6" t="n"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J17" s="6" t="n">
         <v>20</v>
       </c>
@@ -2472,22 +2516,22 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2129A01</t>
+          <t>2129A02</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>2129001</t>
+          <t>2129002</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
+          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2505,7 +2549,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I18" s="6" t="n"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J18" s="6" t="n">
         <v>20</v>
       </c>
@@ -2578,22 +2626,22 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2129A02</t>
+          <t>2129A03</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>2129002</t>
+          <t>2129003</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2611,12 +2659,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I19" s="6" t="n"/>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J19" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
@@ -2684,22 +2736,22 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2129A02</t>
+          <t>2129A03</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>2129002</t>
+          <t>2129003</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2717,12 +2769,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I20" s="6" t="n"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J20" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
@@ -2790,22 +2846,22 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2129A02</t>
+          <t>2129A03</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>2129002</t>
+          <t>2129003</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2823,7 +2879,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I21" s="6" t="n"/>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J21" s="6" t="n">
         <v>15</v>
       </c>
@@ -2896,22 +2956,22 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2129A02</t>
+          <t>2129A03</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>2129002</t>
+          <t>2129003</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2929,7 +2989,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I22" s="6" t="n"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J22" s="6" t="n">
         <v>15</v>
       </c>
@@ -3001,22 +3065,22 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>2129A02</t>
+          <t>2129A03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2129002</t>
+          <t>2129003</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3032,6 +3096,11 @@
       <c r="H23" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -3076,22 +3145,22 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>2129A02</t>
+          <t>2129A03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2129002</t>
+          <t>2129003</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3107,6 +3176,11 @@
       <c r="H24" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -3151,22 +3225,22 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>2129A02</t>
+          <t>2129A04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2129002</t>
+          <t>2129004</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3182,13 +3256,18 @@
       <c r="H25" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3226,22 +3305,22 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>2129A02</t>
+          <t>2129A04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2129002</t>
+          <t>2129004</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3257,13 +3336,18 @@
       <c r="H26" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>20</v>
       </c>
       <c r="K26" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3301,22 +3385,22 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>2129A02</t>
+          <t>2129A04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2129002</t>
+          <t>2129004</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3332,6 +3416,11 @@
       <c r="H27" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -3376,22 +3465,22 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>2129A02</t>
+          <t>2129A04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2129002</t>
+          <t>2129004</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3407,6 +3496,11 @@
       <c r="H28" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -3451,22 +3545,22 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>2129A02</t>
+          <t>2129A04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2129002</t>
+          <t>2129004</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3482,6 +3576,11 @@
       <c r="H29" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -3526,22 +3625,22 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>2129A02</t>
+          <t>2129A04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2129002</t>
+          <t>2129004</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>한화생명 상속H종신보험 무배당 1종(기납입플러스형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
+          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3557,6 +3656,11 @@
       <c r="H30" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -3593,606 +3697,6 @@
         </is>
       </c>
       <c r="AA30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2129A03</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2129003</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>15</v>
-      </c>
-      <c r="K31" t="n">
-        <v>74</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>999</v>
-      </c>
-      <c r="P31" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2129A03</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2129003</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>15</v>
-      </c>
-      <c r="K32" t="n">
-        <v>78</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>999</v>
-      </c>
-      <c r="P32" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2129A03</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2129003</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>20</v>
-      </c>
-      <c r="K33" t="n">
-        <v>74</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O33" t="n">
-        <v>999</v>
-      </c>
-      <c r="P33" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2129A03</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2129003</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(표준체)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>20</v>
-      </c>
-      <c r="K34" t="n">
-        <v>78</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O34" t="n">
-        <v>999</v>
-      </c>
-      <c r="P34" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2129A04</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2129004</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>15</v>
-      </c>
-      <c r="K35" t="n">
-        <v>74</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O35" t="n">
-        <v>999</v>
-      </c>
-      <c r="P35" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2129A04</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2129004</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>15</v>
-      </c>
-      <c r="K36" t="n">
-        <v>78</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>999</v>
-      </c>
-      <c r="P36" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2129A04</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2129004</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>20</v>
-      </c>
-      <c r="K37" t="n">
-        <v>74</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O37" t="n">
-        <v>999</v>
-      </c>
-      <c r="P37" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X37" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2129A04</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2129004</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>한화생명 상속H종신보험 무배당 2종(기본형)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))(건강체)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>20</v>
-      </c>
-      <c r="K38" t="n">
-        <v>78</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O38" t="n">
-        <v>999</v>
-      </c>
-      <c r="P38" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X38" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
